--- a/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 18,47</t>
+          <t>6,81; 17,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 14,08</t>
+          <t>4,06; 14,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 28,38</t>
+          <t>14,13; 27,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,56</t>
+          <t>1,94; 9,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 15,55</t>
+          <t>5,32; 15,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 17,51</t>
+          <t>7,75; 17,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 12,28</t>
+          <t>5,18; 12,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,09</t>
+          <t>5,86; 13,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,82</t>
+          <t>11,62; 19,53</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,88</t>
+          <t>0,67; 6,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,86</t>
+          <t>1,98; 8,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 12,16</t>
+          <t>3,59; 12,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,58</t>
+          <t>1,46; 8,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 12,12</t>
+          <t>3,68; 11,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 14,64</t>
+          <t>4,39; 13,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,08</t>
+          <t>1,71; 5,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 9,02</t>
+          <t>3,83; 8,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,34</t>
+          <t>4,94; 11,25</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,72</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,99</t>
+          <t>1,24; 11,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,3</t>
+          <t>2,03; 12,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 16,27</t>
+          <t>4,27; 17,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,01</t>
+          <t>0,39; 3,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,92</t>
+          <t>1,04; 5,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 12,97</t>
+          <t>4,17; 12,52</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,49</t>
+          <t>0,61; 3,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,96</t>
+          <t>1,25; 5,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,79</t>
+          <t>3,54; 9,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,09</t>
+          <t>1,77; 5,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,35</t>
+          <t>0,37; 3,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,81; 9,37</t>
+          <t>3,72; 9,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,07</t>
+          <t>1,53; 4,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,47</t>
+          <t>1,16; 3,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,55; 8,71</t>
+          <t>4,37; 8,6</t>
         </is>
       </c>
     </row>
@@ -1115,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,43</t>
+          <t>1,48; 6,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,36</t>
+          <t>1,35; 6,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,43</t>
+          <t>0,45; 4,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,17</t>
+          <t>0,81; 5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,16</t>
+          <t>1,06; 4,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,91</t>
+          <t>0,51; 2,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,43</t>
+          <t>1,5; 4,89</t>
         </is>
       </c>
     </row>
@@ -1225,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,48</t>
+          <t>1,0; 8,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,67</t>
+          <t>2,09; 10,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,36</t>
+          <t>0,92; 9,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,94</t>
+          <t>1,72; 10,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,91</t>
+          <t>0,61; 6,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,81</t>
+          <t>1,02; 5,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,98</t>
+          <t>2,56; 8,97</t>
         </is>
       </c>
     </row>
@@ -1335,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,75</t>
+          <t>2,44; 4,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,98</t>
+          <t>2,6; 4,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,13</t>
+          <t>6,11; 9,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,16</t>
+          <t>1,99; 4,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,7</t>
+          <t>2,47; 4,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,22; 8,3</t>
+          <t>5,39; 8,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,07</t>
+          <t>2,46; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,46</t>
+          <t>2,84; 4,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,61</t>
+          <t>6,13; 8,53</t>
         </is>
       </c>
     </row>
@@ -1402,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>10174</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6898</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21064</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>9451</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16178</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14449</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>16349</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>37242</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>6129; 16120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3370; 12041</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14758; 28845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1740; 8670</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5269; 15116</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>10483; 23614</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9304; 22193</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>10676; 23898</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>27852; 46820</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2527</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4783</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6549</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7789</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6132</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>14338</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5895</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2069; 8796</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3398; 11768</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1415; 7744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4119; 12828</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>4198; 13043</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3229; 11094</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8302; 19097</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>9395; 21402</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2982</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3015</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5644</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2795</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8659</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>767; 7369</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1053; 6665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4305</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3400</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2724; 10853</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>679; 6624</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1424; 7956</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4824; 14491</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3245</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6254</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13364</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10976</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9240</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>27459</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1261; 7243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2798; 11173</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7707; 20780</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4019; 13378</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>781; 6791</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8116; 20427</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>6640; 17358</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5003; 15765</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>19060; 37484</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5093</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3711</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3705</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3635</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7416</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2185; 10009</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5301</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1612; 7943</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4420</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>644; 6149</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1321; 8385</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3060; 11549</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1410; 7577</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4225; 13797</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3457</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3344</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>7148</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3651</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>610; 5263</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1438; 7574</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>680; 7080</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4322</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1236; 7642</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>782; 8664</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1313; 6911</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>3609; 12637</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>23251</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24275</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>52125</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>50137</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44223</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>48898</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>102262</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>16453; 32352</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>17420; 32679</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>40177; 64471</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>14262; 29821</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>17393; 33938</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>40296; 64148</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>34255; 56673</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>39034; 61368</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>86079; 119803</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,81; 17,92</t>
+          <t>6,77; 17,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,06; 14,49</t>
+          <t>4,3; 14,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 27,61</t>
+          <t>13,99; 27,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,66</t>
+          <t>2,06; 9,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 15,26</t>
+          <t>5,68; 15,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 17,46</t>
+          <t>7,64; 17,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 12,35</t>
+          <t>4,97; 12,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 13,12</t>
+          <t>5,98; 13,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,62; 19,53</t>
+          <t>12,09; 20,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,38</t>
+          <t>0,67; 6,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,42</t>
+          <t>1,98; 8,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,59; 12,43</t>
+          <t>3,28; 12,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,0</t>
+          <t>1,48; 8,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 11,45</t>
+          <t>3,85; 11,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 13,65</t>
+          <t>4,01; 13,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,86</t>
+          <t>1,53; 5,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,82</t>
+          <t>3,58; 8,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 11,25</t>
+          <t>4,81; 11,2</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 11,92</t>
+          <t>1,22; 11,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,85</t>
+          <t>1,78; 13,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 17,0</t>
+          <t>3,88; 16,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,83</t>
+          <t>0,4; 4,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,82</t>
+          <t>1,05; 5,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 12,52</t>
+          <t>4,08; 12,56</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,51</t>
+          <t>0,62; 3,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,0</t>
+          <t>1,27; 5,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 9,54</t>
+          <t>3,53; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,88</t>
+          <t>1,72; 5,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,25</t>
+          <t>0,37; 3,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 9,36</t>
+          <t>3,96; 10,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,0</t>
+          <t>1,43; 3,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,65</t>
+          <t>1,19; 3,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,6</t>
+          <t>4,37; 8,67</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,78</t>
+          <t>1,49; 6,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,65</t>
+          <t>1,42; 6,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,32</t>
+          <t>0,46; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,16</t>
+          <t>0,86; 5,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,01</t>
+          <t>1,16; 4,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,73</t>
+          <t>0,51; 2,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,89</t>
+          <t>1,42; 4,6</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>0,0; 7,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,62</t>
+          <t>0,98; 8,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,99</t>
+          <t>2,24; 11,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,56</t>
+          <t>0,94; 11,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,61</t>
+          <t>1,54; 11,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 6,81</t>
+          <t>0,63; 6,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,36</t>
+          <t>1,01; 6,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,97</t>
+          <t>2,57; 8,9</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,79</t>
+          <t>2,38; 4,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,88</t>
+          <t>2,62; 4,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 9,81</t>
+          <t>6,13; 9,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,17</t>
+          <t>1,87; 4,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,81</t>
+          <t>2,44; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,58</t>
+          <t>5,18; 8,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,07</t>
+          <t>2,48; 4,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,46</t>
+          <t>2,78; 4,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 8,53</t>
+          <t>6,27; 8,55</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6129; 16120</t>
+          <t>6092; 15789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3370; 12041</t>
+          <t>3573; 11875</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14758; 28845</t>
+          <t>14610; 28975</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1740; 8670</t>
+          <t>1846; 8663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5269; 15116</t>
+          <t>5628; 15122</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10483; 23614</t>
+          <t>10333; 23136</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9304; 22193</t>
+          <t>8930; 21941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10676; 23898</t>
+          <t>10893; 24234</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>27852; 46820</t>
+          <t>28993; 47943</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>622; 5895</t>
+          <t>623; 6202</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2069; 8796</t>
+          <t>2067; 9349</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3398; 11768</t>
+          <t>3106; 11463</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1415; 7744</t>
+          <t>1436; 8140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4119; 12828</t>
+          <t>4315; 13154</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4198; 13043</t>
+          <t>3830; 12908</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3229; 11094</t>
+          <t>2893; 10895</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8302; 19097</t>
+          <t>7760; 19017</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9395; 21402</t>
+          <t>9145; 21302</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5188</t>
+          <t>0; 4991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>767; 7369</t>
+          <t>757; 7386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1053; 6665</t>
+          <t>925; 6923</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4305</t>
+          <t>0; 5270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3400</t>
+          <t>0; 3147</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2724; 10853</t>
+          <t>2478; 10514</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>679; 6624</t>
+          <t>698; 6927</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1424; 7956</t>
+          <t>1430; 8097</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4824; 14491</t>
+          <t>4725; 14533</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1261; 7243</t>
+          <t>1269; 7288</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2798; 11173</t>
+          <t>2831; 11453</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7707; 20780</t>
+          <t>7694; 21414</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4019; 13378</t>
+          <t>3912; 12779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>781; 6791</t>
+          <t>767; 7451</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8116; 20427</t>
+          <t>8638; 21942</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6640; 17358</t>
+          <t>6187; 16646</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5003; 15765</t>
+          <t>5154; 15145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19060; 37484</t>
+          <t>19072; 37823</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2185; 10009</t>
+          <t>2193; 10026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 4964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1612; 7943</t>
+          <t>1701; 7298</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4420</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>644; 6149</t>
+          <t>654; 6076</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1321; 8385</t>
+          <t>1392; 8673</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3060; 11549</t>
+          <t>3337; 11742</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1410; 7577</t>
+          <t>1419; 8052</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4225; 13797</t>
+          <t>4001; 12968</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3651</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>610; 5263</t>
+          <t>601; 4907</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1438; 7574</t>
+          <t>1544; 7766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>680; 7080</t>
+          <t>694; 8224</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 5654</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1236; 7642</t>
+          <t>1111; 7929</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>782; 8664</t>
+          <t>797; 8293</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1313; 6911</t>
+          <t>1297; 7785</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3609; 12637</t>
+          <t>3627; 12539</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16453; 32352</t>
+          <t>16063; 31717</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17420; 32679</t>
+          <t>17534; 33253</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40177; 64471</t>
+          <t>40282; 64576</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14262; 29821</t>
+          <t>13365; 29286</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17393; 33938</t>
+          <t>17187; 32832</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40296; 64148</t>
+          <t>38709; 62687</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34255; 56673</t>
+          <t>34530; 55707</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>39034; 61368</t>
+          <t>38187; 61708</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>86079; 119803</t>
+          <t>88109; 120083</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$colectiva-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,31%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 17,56</t>
+          <t>1,83; 9,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,29</t>
+          <t>5,19; 15,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 27,74</t>
+          <t>7,61; 17,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,65</t>
+          <t>6,78; 18,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,27</t>
+          <t>4,14; 14,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 17,11</t>
+          <t>14,55; 29,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,21</t>
+          <t>5,22; 12,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,31</t>
+          <t>6,05; 13,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>12,09; 20,0</t>
+          <t>12,42; 20,63</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>2,73%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,41%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,71</t>
+          <t>1,48; 8,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 8,95</t>
+          <t>3,78; 12,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 12,11</t>
+          <t>4,11; 14,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,41</t>
+          <t>0,68; 6,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,74</t>
+          <t>2,04; 8,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,01; 13,51</t>
+          <t>3,19; 12,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,76</t>
+          <t>1,66; 6,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,78</t>
+          <t>3,69; 9,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,2</t>
+          <t>4,77; 11,2</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,65%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,79</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,94</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 13,35</t>
+          <t>4,12; 16,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,21</t>
+          <t>1,22; 10,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 16,47</t>
+          <t>1,97; 12,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 4,0</t>
+          <t>0,44; 4,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,93</t>
+          <t>1,04; 5,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 12,56</t>
+          <t>4,25; 13,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,54</t>
+          <t>1,85; 6,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 5,12</t>
+          <t>0,38; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 9,83</t>
+          <t>3,89; 9,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,62</t>
+          <t>0,59; 3,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,57</t>
+          <t>1,51; 4,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 10,05</t>
+          <t>5,18; 11,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,84</t>
+          <t>1,58; 4,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,5</t>
+          <t>1,25; 3,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,67</t>
+          <t>5,22; 9,54</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,8</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,46; 4,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,11</t>
+          <t>0,84; 5,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>1,37; 6,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,27</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,33</t>
+          <t>1,26; 6,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,08</t>
+          <t>1,08; 4,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,9</t>
+          <t>0,48; 2,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,6</t>
+          <t>1,46; 4,52</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,37</t>
+          <t>0,92; 9,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,03</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 11,27</t>
+          <t>1,07; 8,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,11</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,98; 8,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 11,01</t>
+          <t>2,28; 11,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,52</t>
+          <t>0,78; 6,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,04</t>
+          <t>1,0; 5,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,9</t>
+          <t>2,41; 8,43</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>3,44%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,7</t>
+          <t>2,01; 4,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,97</t>
+          <t>2,47; 4,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 9,83</t>
+          <t>5,13; 8,23</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,09</t>
+          <t>2,5; 4,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,66</t>
+          <t>2,55; 4,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,39</t>
+          <t>6,76; 10,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,01</t>
+          <t>2,44; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,49</t>
+          <t>2,83; 4,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,55</t>
+          <t>6,52; 8,85</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción colectiva en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9451</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14531</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>10174</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>6898</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>9451</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16178</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>35770</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6092; 15789</t>
+          <t>1645; 8583</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3573; 11875</t>
+          <t>5138; 15402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14610; 28975</t>
+          <t>9208; 21366</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1846; 8663</t>
+          <t>6095; 16607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5628; 15122</t>
+          <t>3443; 11699</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10333; 23136</t>
+          <t>14979; 29904</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8930; 21941</t>
+          <t>9374; 22066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10893; 24234</t>
+          <t>11019; 23846</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28993; 47943</t>
+          <t>27805; 46189</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3606</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7874</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7183</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2527</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4783</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6549</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3606</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7874</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7789</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14338</t>
+          <t>13923</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>623; 6202</t>
+          <t>1428; 8304</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2067; 9349</t>
+          <t>4236; 13587</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3106; 11463</t>
+          <t>3755; 13175</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1436; 8140</t>
+          <t>625; 6364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4315; 13154</t>
+          <t>2134; 9250</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3830; 12908</t>
+          <t>3084; 11828</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2893; 10895</t>
+          <t>3136; 11511</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7760; 19017</t>
+          <t>7981; 19527</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9145; 21302</t>
+          <t>8959; 21052</t>
         </is>
       </c>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5019</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1422</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>2982</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3015</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1373</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>8013</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4991</t>
+          <t>0; 4421</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>757; 7386</t>
+          <t>0; 3443</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>925; 6923</t>
+          <t>2344; 9437</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5270</t>
+          <t>0; 4930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3147</t>
+          <t>752; 6797</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2478; 10514</t>
+          <t>1054; 6513</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>698; 6927</t>
+          <t>761; 6941</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1430; 8097</t>
+          <t>1419; 8088</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4725; 14533</t>
+          <t>4696; 14383</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7731</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2986</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12619</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>3245</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6254</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7731</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>14392</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>27459</t>
+          <t>27011</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1269; 7288</t>
+          <t>4202; 13849</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2831; 11453</t>
+          <t>788; 6995</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7694; 21414</t>
+          <t>7855; 19323</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3912; 12779</t>
+          <t>1225; 7203</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>767; 7451</t>
+          <t>3374; 11091</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8638; 21942</t>
+          <t>9256; 20962</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6187; 16646</t>
+          <t>6871; 17657</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5154; 15145</t>
+          <t>5390; 15018</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19072; 37823</t>
+          <t>19851; 36288</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2212</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>5093</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1423</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2212</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7081</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2193; 10026</t>
+          <t>0; 4763</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4964</t>
+          <t>654; 6315</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1701; 7298</t>
+          <t>1240; 7478</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 4445</t>
+          <t>2019; 9493</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>654; 6076</t>
+          <t>0; 4374</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1392; 8673</t>
+          <t>1491; 7665</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3337; 11742</t>
+          <t>3098; 11965</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1419; 8052</t>
+          <t>1346; 8090</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4001; 12968</t>
+          <t>3896; 12073</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1408</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1936</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1408</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6439</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>680; 6929</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>601; 4907</t>
+          <t>0; 4397</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1544; 7766</t>
+          <t>729; 5865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>694; 8224</t>
+          <t>0; 3521</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 5654</t>
+          <t>600; 5182</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1111; 7929</t>
+          <t>1601; 8201</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>797; 8293</t>
+          <t>991; 8796</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1297; 7785</t>
+          <t>1290; 7486</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3627; 12539</t>
+          <t>3340; 11686</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>20972</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>24622</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>45312</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>23251</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>24275</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>52125</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>20972</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>24622</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>52924</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>102262</t>
+          <t>98236</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16063; 31717</t>
+          <t>14395; 29740</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17534; 33253</t>
+          <t>17413; 33109</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40282; 64576</t>
+          <t>35283; 56632</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13365; 29286</t>
+          <t>16912; 32063</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17187; 32832</t>
+          <t>17086; 33340</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38709; 62687</t>
+          <t>41957; 66857</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34530; 55707</t>
+          <t>33934; 56566</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38187; 61708</t>
+          <t>38928; 61349</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>88109; 120083</t>
+          <t>85252; 115794</t>
         </is>
       </c>
     </row>
